--- a/docs/federal-funding/multiyear_funding_stack.xlsx
+++ b/docs/federal-funding/multiyear_funding_stack.xlsx
@@ -12,6 +12,7 @@
     <sheet name="ExampleA_RuralTown" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ExampleB_CapitalDeal" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="PublicLogic_Revenue" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GrantWriting_Hours" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -111,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,6 +137,19 @@
     <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -703,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1376,6 +1392,156 @@
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>tax-exempt sponsor monetizes via IRC 6417</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>gw_prin</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GW: Principal (Boudreau) hourly rate</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>185</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>$/hr</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>governance/systems; MPA/MCPPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>gw_anal</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GW: Analyst hourly rate</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>$/hr</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>grant analyst / budget build</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>gw_sme</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GW: Behavioral/org SME (Rothschild) rate</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>$/hr</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>sustainability/behavioral-systems narrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>gw_fixed</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GW: agreed fixed fee, writing block (non-contingent)</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>12500</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>fixed-fee, owed regardless of award (2 CFR 200.459 bars contingent fees)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>gw_winprob</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GW: client's expected win probability</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>prob</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>planning assumption only; fee is NOT contingent on it</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>gw_award</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GW: target award size (if won)</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>750000</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>illustrative federal capital award being pursued</t>
         </is>
       </c>
     </row>
@@ -2839,4 +3005,823 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grant-writing hours -- an org working with PublicLogic (the work, shown line by line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Hours x rate = line cost (live formulas). Funding route per line follows the cost principles: writing = proposal cost (2 CFR 200.460, indirect/own-source, non-contingent); post-award = allowable grant-admin on the won award. Not legal/accounting advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Task (the work)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Hours</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Rate $/hr</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Line cost</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Deliverable</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Funding route / allowability</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>1. Discover/eligibility</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Review Stewardship Map; confirm Assistance Listing eligibility</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="11">
+        <f>Inputs!$C$30</f>
+        <v/>
+      </c>
+      <c r="F5" s="11">
+        <f>D5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Eligibility memo</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>1. Discover/eligibility</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>SAM.gov / UEI registration check; portal setup</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="11">
+        <f>Inputs!$C$31</f>
+        <v/>
+      </c>
+      <c r="F6" s="11">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Registration confirmed</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>2. Narrative</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Need statement &amp; problem analysis</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="11">
+        <f>Inputs!$C$30</f>
+        <v/>
+      </c>
+      <c r="F7" s="11">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Need statement</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>2. Narrative</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Project design &amp; logic model</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="11">
+        <f>Inputs!$C$30</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>Project narrative</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>2. Narrative</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Behavioral/organizational sustainability section</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Behav/org SME</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="11">
+        <f>Inputs!$C$32</f>
+        <v/>
+      </c>
+      <c r="F9" s="11">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>Sustainability narrative</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>3. Budget</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Budget build (cost principles, MTDC, 15% de minimis)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="11">
+        <f>Inputs!$C$31</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>D10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>SF-424A budget</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>3. Budget</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Match/cost-share strategy &amp; budget narrative</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="11">
+        <f>Inputs!$C$30</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Budget narrative</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>4. Attachments/compliance</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>SF-424 family, certifications, reps &amp; certs</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="11">
+        <f>Inputs!$C$31</f>
+        <v/>
+      </c>
+      <c r="F12" s="11">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>Forms package</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>4. Attachments/compliance</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Letters of support, MOUs, env-review coordination</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="11">
+        <f>Inputs!$C$31</f>
+        <v/>
+      </c>
+      <c r="F13" s="11">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>Attachments</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>5. Review/submit</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Internal review &amp; responsiveness check</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="11">
+        <f>Inputs!$C$30</f>
+        <v/>
+      </c>
+      <c r="F14" s="11">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>Reviewed package</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>5. Review/submit</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Portal submission (grants.gov / state e-grants)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="11">
+        <f>Inputs!$C$31</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>Submission receipt</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>Proposal cost - 2 CFR 200.460: indirect/F&amp;A or org own-source; NON-FederalAward; non-contingent</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>6. Post-award (if won)</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Award setup, drawdown &amp; subrecipient-monitoring setup</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="11">
+        <f>Inputs!$C$30</f>
+        <v/>
+      </c>
+      <c r="F16" s="11">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>Grants-mgmt setup</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>ALLOWABLE on the WON award as grant-administration (200.413 / program admin line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>6. Post-award (if won)</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Compliance calendar &amp; reporting cadence</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="11">
+        <f>Inputs!$C$31</f>
+        <v/>
+      </c>
+      <c r="F17" s="11">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>Compliance plan</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>ALLOWABLE on the WON award as grant-administration (200.413 / program admin line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>WRITING subtotal (proposal cost - own-source / F&amp;A, non-contingent)</t>
+        </is>
+      </c>
+      <c r="D18" s="19">
+        <f>SUM(D5:D15)</f>
+        <v/>
+      </c>
+      <c r="F18" s="13">
+        <f>SUM(F5:F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>POST-AWARD subtotal (allowable grant-admin on the WON award)</t>
+        </is>
+      </c>
+      <c r="D19" s="19">
+        <f>SUM(D16:D17)</f>
+        <v/>
+      </c>
+      <c r="F19" s="13">
+        <f>SUM(F16:F17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ENGAGEMENT TOTAL (time &amp; materials reference)</t>
+        </is>
+      </c>
+      <c r="D20" s="19">
+        <f>D18+D19</f>
+        <v/>
+      </c>
+      <c r="F20" s="13">
+        <f>F18+F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>FIXED-FEE RECONCILIATION (writing block)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Agreed fixed fee for the writing block (non-contingent)</t>
+        </is>
+      </c>
+      <c r="F23" s="15">
+        <f>Inputs!$C$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Time &amp; materials value of writing hours (from above)</t>
+        </is>
+      </c>
+      <c r="F24" s="15">
+        <f>F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Fixed-fee variance vs. T&amp;M (org's certainty premium / discount)</t>
+        </is>
+      </c>
+      <c r="F25" s="15">
+        <f>Inputs!$C$33-F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Writing hours (from above)</t>
+        </is>
+      </c>
+      <c r="F26" s="20">
+        <f>D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Effective blended rate on the fixed fee</t>
+        </is>
+      </c>
+      <c r="F27" s="15">
+        <f>Inputs!$C$33/D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>WHY NON-CONTINGENT (what PublicLogic does NOT do)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Target award if won (illustrative)</t>
+        </is>
+      </c>
+      <c r="F30" s="15">
+        <f>Inputs!$C$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Client's expected win probability (planning only)</t>
+        </is>
+      </c>
+      <c r="F31" s="21">
+        <f>Inputs!$C$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A contingent 'X% of award' fee would be barred by 2 CFR 200.459(b).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>PublicLogic charges the FIXED writing fee regardless of outcome -&gt; allowable professional service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Expected-value of award to the org (context, not a fee basis)</t>
+        </is>
+      </c>
+      <c r="F34" s="15">
+        <f>Inputs!$C$35*Inputs!$C$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>FUNDING-ROUTE NOTES (subject to the funding source, approved budget, and cost principles; not legal/accounting advice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 2 CFR 200.460 -- Proposal costs (preparing bids/proposals/applications, successful OR unsuccessful) are normally</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    treated as INDIRECT (F&amp;A) costs and allocated to current activities; they are NOT directly chargeable to the</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    federal award being sought. The org pays the writing fee from own-source / unrestricted funds or its F&amp;A pool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 2 CFR 200.459(b) -- professional-service costs are allowable; CONTINGENT fees are a factor against allowability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PublicLogic's writing fee is fixed and NON-CONTINGENT, which is what keeps it an allowable professional service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * 2 CFR 200.458 -- Pre-award costs are allowable only with prior written approval and only if necessary for the</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    award; a 90-day-before-award window is typical. Post-award, grant-ADMINISTRATION (a different activity from</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    writing) is allowable on the won award (200.413 direct admin / program admin line, e.g., CDBG's planning+admin).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Where an org has a capacity-building or planning grant (or foundation/own-source capacity funds), some writing</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    support may be an allowable activity of THAT award -- never of the prospective award it is being written for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Hours and rates here are illustrative planning assumptions, not quotes. Edit them on the Inputs sheet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>